--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/25.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/25.xlsx
@@ -426,13 +426,13 @@
         <v>-10.5570790891649</v>
       </c>
       <c r="E2">
-        <v>-12.15565896595032</v>
+        <v>-8.363864243819684</v>
       </c>
       <c r="F2">
-        <v>2.51885223424327</v>
+        <v>2.41353360265134</v>
       </c>
       <c r="G2">
-        <v>-18.31361173044231</v>
+        <v>-19.75492614954437</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.07669754642888</v>
       </c>
       <c r="E3">
-        <v>-11.15485963300639</v>
+        <v>-9.359879077317414</v>
       </c>
       <c r="F3">
-        <v>2.767925744917024</v>
+        <v>2.255887002224566</v>
       </c>
       <c r="G3">
-        <v>-18.32851647131297</v>
+        <v>-19.23681148440113</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.452990930979288</v>
       </c>
       <c r="E4">
-        <v>-12.57421545005522</v>
+        <v>-10.05562503845269</v>
       </c>
       <c r="F4">
-        <v>2.584675964804524</v>
+        <v>2.070256494196419</v>
       </c>
       <c r="G4">
-        <v>-17.80429201114038</v>
+        <v>-18.81400466130107</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.762263297575865</v>
       </c>
       <c r="E5">
-        <v>-11.76500375552562</v>
+        <v>-10.43893737125509</v>
       </c>
       <c r="F5">
-        <v>3.268466748058626</v>
+        <v>2.178124840654165</v>
       </c>
       <c r="G5">
-        <v>-17.23151814455145</v>
+        <v>-18.25234930323954</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.03787291164163</v>
       </c>
       <c r="E6">
-        <v>-13.39190384889879</v>
+        <v>-10.49780498857321</v>
       </c>
       <c r="F6">
-        <v>3.031800524344002</v>
+        <v>2.394908589966796</v>
       </c>
       <c r="G6">
-        <v>-16.70074071545516</v>
+        <v>-17.51287547839113</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.326880495652333</v>
       </c>
       <c r="E7">
-        <v>-14.58554093686583</v>
+        <v>-12.16055144889097</v>
       </c>
       <c r="F7">
-        <v>2.983395703528815</v>
+        <v>2.440871383678529</v>
       </c>
       <c r="G7">
-        <v>-16.68665966450299</v>
+        <v>-17.11229066056448</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.666712004624721</v>
       </c>
       <c r="E8">
-        <v>-14.39619187935557</v>
+        <v>-12.50414662179403</v>
       </c>
       <c r="F8">
-        <v>2.674976295383698</v>
+        <v>2.630718281786926</v>
       </c>
       <c r="G8">
-        <v>-15.15356778273108</v>
+        <v>-16.66727619128627</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.081491341294236</v>
       </c>
       <c r="E9">
-        <v>-14.81330304591943</v>
+        <v>-12.83504958088842</v>
       </c>
       <c r="F9">
-        <v>3.415475454298649</v>
+        <v>2.436529081753054</v>
       </c>
       <c r="G9">
-        <v>-15.97011339865374</v>
+        <v>-16.38877501202926</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.588477344085019</v>
       </c>
       <c r="E10">
-        <v>-15.94002359302084</v>
+        <v>-12.93716874094331</v>
       </c>
       <c r="F10">
-        <v>3.396459452199983</v>
+        <v>2.53828407677814</v>
       </c>
       <c r="G10">
-        <v>-15.26869900845459</v>
+        <v>-15.77343426025452</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.183799634737174</v>
       </c>
       <c r="E11">
-        <v>-15.40230316958396</v>
+        <v>-13.96403362816186</v>
       </c>
       <c r="F11">
-        <v>3.388309973691241</v>
+        <v>3.14690714516741</v>
       </c>
       <c r="G11">
-        <v>-14.68988387888182</v>
+        <v>-15.57561161572439</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.865644136184152</v>
       </c>
       <c r="E12">
-        <v>-16.88934802480485</v>
+        <v>-14.14031252963289</v>
       </c>
       <c r="F12">
-        <v>4.004544081777433</v>
+        <v>3.37422772784365</v>
       </c>
       <c r="G12">
-        <v>-13.80081569433491</v>
+        <v>-15.0201861469434</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.611652775312674</v>
       </c>
       <c r="E13">
-        <v>-18.56754443125097</v>
+        <v>-15.29729752765832</v>
       </c>
       <c r="F13">
-        <v>4.506508220117044</v>
+        <v>3.225840618245369</v>
       </c>
       <c r="G13">
-        <v>-13.84454175011918</v>
+        <v>-14.72113188089285</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.41062950058476</v>
       </c>
       <c r="E14">
-        <v>-17.93682529982853</v>
+        <v>-15.47914588551594</v>
       </c>
       <c r="F14">
-        <v>4.264914867090568</v>
+        <v>3.407617561115693</v>
       </c>
       <c r="G14">
-        <v>-12.51323170704982</v>
+        <v>-14.3357951168506</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.235632869244763</v>
       </c>
       <c r="E15">
-        <v>-19.63614493907273</v>
+        <v>-17.06686458325067</v>
       </c>
       <c r="F15">
-        <v>4.310914108968024</v>
+        <v>3.725935959724264</v>
       </c>
       <c r="G15">
-        <v>-13.17324099340622</v>
+        <v>-14.03279732109517</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.074834930110018</v>
       </c>
       <c r="E16">
-        <v>-19.97183655082464</v>
+        <v>-17.56672433225041</v>
       </c>
       <c r="F16">
-        <v>4.27034233031371</v>
+        <v>3.984590367778798</v>
       </c>
       <c r="G16">
-        <v>-11.76501319319348</v>
+        <v>-13.87786268333556</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.907296569351162</v>
       </c>
       <c r="E17">
-        <v>-20.08525659889439</v>
+        <v>-18.36294893496726</v>
       </c>
       <c r="F17">
-        <v>5.057152197249571</v>
+        <v>4.384189832684863</v>
       </c>
       <c r="G17">
-        <v>-11.75838451267665</v>
+        <v>-13.88580065226484</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.726787557195821</v>
       </c>
       <c r="E18">
-        <v>-20.77661676887064</v>
+        <v>-20.0333705298133</v>
       </c>
       <c r="F18">
-        <v>4.814786805803686</v>
+        <v>4.44075241568282</v>
       </c>
       <c r="G18">
-        <v>-11.2436344446252</v>
+        <v>-13.2895548864295</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.5220022594549</v>
       </c>
       <c r="E19">
-        <v>-22.76730079539686</v>
+        <v>-21.56120407345533</v>
       </c>
       <c r="F19">
-        <v>5.133395133003237</v>
+        <v>4.642121904364156</v>
       </c>
       <c r="G19">
-        <v>-11.02653797815118</v>
+        <v>-12.63934894601273</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.293629802527656</v>
       </c>
       <c r="E20">
-        <v>-22.54547777853777</v>
+        <v>-21.11478784778348</v>
       </c>
       <c r="F20">
-        <v>5.22022129069507</v>
+        <v>4.970397279154378</v>
       </c>
       <c r="G20">
-        <v>-10.83658150707407</v>
+        <v>-13.00092662890356</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.038554336336593</v>
       </c>
       <c r="E21">
-        <v>-22.45509974689817</v>
+        <v>-22.01793687605805</v>
       </c>
       <c r="F21">
-        <v>5.651519062636661</v>
+        <v>4.949863707973784</v>
       </c>
       <c r="G21">
-        <v>-11.00028694128754</v>
+        <v>-11.9615774588307</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.763681715481135</v>
       </c>
       <c r="E22">
-        <v>-23.6342628933982</v>
+        <v>-22.40729213133807</v>
       </c>
       <c r="F22">
-        <v>5.367892690857333</v>
+        <v>4.935166813513315</v>
       </c>
       <c r="G22">
-        <v>-10.56228493198105</v>
+        <v>-11.66492116168709</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.474156210671957</v>
       </c>
       <c r="E23">
-        <v>-24.1168868153999</v>
+        <v>-22.84067557987261</v>
       </c>
       <c r="F23">
-        <v>6.030213847765677</v>
+        <v>4.79424992115348</v>
       </c>
       <c r="G23">
-        <v>-10.37085208483767</v>
+        <v>-11.44250660848096</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.181674239928842</v>
       </c>
       <c r="E24">
-        <v>-25.31638408454628</v>
+        <v>-23.65168146169453</v>
       </c>
       <c r="F24">
-        <v>5.809377725118551</v>
+        <v>5.0584626744808</v>
       </c>
       <c r="G24">
-        <v>-9.263382061521186</v>
+        <v>-11.27913534957516</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.893724012853787</v>
       </c>
       <c r="E25">
-        <v>-25.63889340355319</v>
+        <v>-24.06167402404763</v>
       </c>
       <c r="F25">
-        <v>5.192774165170711</v>
+        <v>4.726090194516331</v>
       </c>
       <c r="G25">
-        <v>-9.753931832585303</v>
+        <v>-11.13914200311049</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.619943149377248</v>
       </c>
       <c r="E26">
-        <v>-25.51465839319359</v>
+        <v>-25.03964315433898</v>
       </c>
       <c r="F26">
-        <v>6.12771600454479</v>
+        <v>4.659136570817658</v>
       </c>
       <c r="G26">
-        <v>-9.420376576763193</v>
+        <v>-11.00767926459727</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.365548462845976</v>
       </c>
       <c r="E27">
-        <v>-24.59829799969475</v>
+        <v>-25.12854679595826</v>
       </c>
       <c r="F27">
-        <v>5.445845376930377</v>
+        <v>5.064140304659587</v>
       </c>
       <c r="G27">
-        <v>-9.788274872309104</v>
+        <v>-10.16426386534287</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.136404675785754</v>
       </c>
       <c r="E28">
-        <v>-26.82581890201931</v>
+        <v>-25.7034301543297</v>
       </c>
       <c r="F28">
-        <v>5.280811396005437</v>
+        <v>4.641921439452679</v>
       </c>
       <c r="G28">
-        <v>-8.818184840121594</v>
+        <v>-9.983691715698525</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.9357066774363745</v>
       </c>
       <c r="E29">
-        <v>-26.40384017178276</v>
+        <v>-26.39069525793968</v>
       </c>
       <c r="F29">
-        <v>5.118832434062021</v>
+        <v>4.595383758763403</v>
       </c>
       <c r="G29">
-        <v>-8.889761013831556</v>
+        <v>-9.760315103110576</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.766915490543321</v>
       </c>
       <c r="E30">
-        <v>-26.40165973583722</v>
+        <v>-26.10878357963297</v>
       </c>
       <c r="F30">
-        <v>5.122889777600934</v>
+        <v>4.575642106819885</v>
       </c>
       <c r="G30">
-        <v>-9.038317602555084</v>
+        <v>-9.51278910305483</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.6322958378965231</v>
       </c>
       <c r="E31">
-        <v>-25.97006632138369</v>
+        <v>-27.1877837286121</v>
       </c>
       <c r="F31">
-        <v>5.11546760567185</v>
+        <v>4.358904746081811</v>
       </c>
       <c r="G31">
-        <v>-9.261241250956473</v>
+        <v>-8.9775003073051</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.5333872412902612</v>
       </c>
       <c r="E32">
-        <v>-27.0816816388967</v>
+        <v>-26.42671190654859</v>
       </c>
       <c r="F32">
-        <v>4.945905768523208</v>
+        <v>4.060478762284067</v>
       </c>
       <c r="G32">
-        <v>-8.490891455201268</v>
+        <v>-8.803350589354888</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.471785336608662</v>
       </c>
       <c r="E33">
-        <v>-26.63746661522701</v>
+        <v>-27.6491639746873</v>
       </c>
       <c r="F33">
-        <v>5.441019308441667</v>
+        <v>4.205416550017091</v>
       </c>
       <c r="G33">
-        <v>-7.921565076844898</v>
+        <v>-9.070466311450053</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.4479891882583987</v>
       </c>
       <c r="E34">
-        <v>-28.1165996028741</v>
+        <v>-26.94433494038462</v>
       </c>
       <c r="F34">
-        <v>4.629143043897094</v>
+        <v>4.324611992340717</v>
       </c>
       <c r="G34">
-        <v>-8.615814278513742</v>
+        <v>-8.295936713604474</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.4626681055413253</v>
       </c>
       <c r="E35">
-        <v>-25.08252921447916</v>
+        <v>-26.84233622345815</v>
       </c>
       <c r="F35">
-        <v>4.758853782031857</v>
+        <v>4.540448089344546</v>
       </c>
       <c r="G35">
-        <v>-7.641287285893636</v>
+        <v>-8.175415605672615</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.5136471918871884</v>
       </c>
       <c r="E36">
-        <v>-25.71906699496768</v>
+        <v>-26.59063085111692</v>
       </c>
       <c r="F36">
-        <v>5.047881109277438</v>
+        <v>4.469649184162077</v>
       </c>
       <c r="G36">
-        <v>-8.16312291476536</v>
+        <v>-8.111283970164214</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.597669339111859</v>
       </c>
       <c r="E37">
-        <v>-25.66251271635749</v>
+        <v>-26.34525912604605</v>
       </c>
       <c r="F37">
-        <v>5.288379360597413</v>
+        <v>4.214516994304246</v>
       </c>
       <c r="G37">
-        <v>-8.922053313679037</v>
+        <v>-8.161634790348424</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.7082115284128616</v>
       </c>
       <c r="E38">
-        <v>-25.16966774128538</v>
+        <v>-26.36130298139387</v>
       </c>
       <c r="F38">
-        <v>5.346721276776583</v>
+        <v>4.46813824201937</v>
       </c>
       <c r="G38">
-        <v>-8.376308485841896</v>
+        <v>-8.332121633637305</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.839136956481125</v>
       </c>
       <c r="E39">
-        <v>-25.6840595767107</v>
+        <v>-27.08864242107711</v>
       </c>
       <c r="F39">
-        <v>5.748807500625851</v>
+        <v>4.613263240785427</v>
       </c>
       <c r="G39">
-        <v>-8.441267727385682</v>
+        <v>-8.090311858863801</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.9838832240286035</v>
       </c>
       <c r="E40">
-        <v>-25.69775271444866</v>
+        <v>-26.14983807357889</v>
       </c>
       <c r="F40">
-        <v>5.378974589971984</v>
+        <v>4.749322586695246</v>
       </c>
       <c r="G40">
-        <v>-8.531865786186495</v>
+        <v>-7.834902715515188</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.137635660725903</v>
       </c>
       <c r="E41">
-        <v>-24.68702305322706</v>
+        <v>-25.70774118768487</v>
       </c>
       <c r="F41">
-        <v>6.078206141614269</v>
+        <v>5.059180040651624</v>
       </c>
       <c r="G41">
-        <v>-8.787101315019799</v>
+        <v>-8.280413226265715</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.296433211928026</v>
       </c>
       <c r="E42">
-        <v>-23.97825262137712</v>
+        <v>-25.64012690731666</v>
       </c>
       <c r="F42">
-        <v>6.144420861589645</v>
+        <v>5.322824533940622</v>
       </c>
       <c r="G42">
-        <v>-8.034205652228481</v>
+        <v>-8.129878998514418</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.45742056734623</v>
       </c>
       <c r="E43">
-        <v>-24.37762542237263</v>
+        <v>-25.76939560980195</v>
       </c>
       <c r="F43">
-        <v>5.294179589151815</v>
+        <v>5.365357886604766</v>
       </c>
       <c r="G43">
-        <v>-8.544388222617771</v>
+        <v>-8.493760663506901</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.619204315477783</v>
       </c>
       <c r="E44">
-        <v>-21.98180809074336</v>
+        <v>-25.39143676639726</v>
       </c>
       <c r="F44">
-        <v>6.072263433866586</v>
+        <v>5.237845635557032</v>
       </c>
       <c r="G44">
-        <v>-8.156872792214234</v>
+        <v>-8.896654684924391</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.780133935988971</v>
       </c>
       <c r="E45">
-        <v>-24.43368962204649</v>
+        <v>-24.20664186534077</v>
       </c>
       <c r="F45">
-        <v>5.657410411605371</v>
+        <v>5.594316980003743</v>
       </c>
       <c r="G45">
-        <v>-9.033130053052542</v>
+        <v>-8.9029974889085</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.940221480189716</v>
       </c>
       <c r="E46">
-        <v>-23.3575053503456</v>
+        <v>-24.27685190278699</v>
       </c>
       <c r="F46">
-        <v>5.798275945186232</v>
+        <v>5.367054383045699</v>
       </c>
       <c r="G46">
-        <v>-9.173067268508509</v>
+        <v>-9.114867244711116</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.097975756501864</v>
       </c>
       <c r="E47">
-        <v>-22.94734665953951</v>
+        <v>-22.94558569793778</v>
       </c>
       <c r="F47">
-        <v>5.80844829689261</v>
+        <v>5.95549179456355</v>
       </c>
       <c r="G47">
-        <v>-9.601944725469053</v>
+        <v>-8.979141160280614</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.253560995737744</v>
       </c>
       <c r="E48">
-        <v>-21.99197099885522</v>
+        <v>-22.97996598128471</v>
       </c>
       <c r="F48">
-        <v>5.65908205702422</v>
+        <v>5.620064295617557</v>
       </c>
       <c r="G48">
-        <v>-10.00394326149179</v>
+        <v>-9.485112599644438</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.404932596056716</v>
       </c>
       <c r="E49">
-        <v>-21.65797805053516</v>
+        <v>-22.10757563608182</v>
       </c>
       <c r="F49">
-        <v>5.584461064645235</v>
+        <v>5.836914314322413</v>
       </c>
       <c r="G49">
-        <v>-9.376933786767069</v>
+        <v>-8.934879901855176</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.552954515968616</v>
       </c>
       <c r="E50">
-        <v>-21.69108745121669</v>
+        <v>-22.6901922739401</v>
       </c>
       <c r="F50">
-        <v>5.581821886099916</v>
+        <v>5.989237825818797</v>
       </c>
       <c r="G50">
-        <v>-9.535056143672435</v>
+        <v>-9.586859843221601</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.695464928874865</v>
       </c>
       <c r="E51">
-        <v>-19.88474786255431</v>
+        <v>-22.65528868596624</v>
       </c>
       <c r="F51">
-        <v>6.098791071573837</v>
+        <v>5.781431922417707</v>
       </c>
       <c r="G51">
-        <v>-9.57188330687468</v>
+        <v>-9.701779598633225</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.832887828018885</v>
       </c>
       <c r="E52">
-        <v>-19.70182797617489</v>
+        <v>-21.41533913851602</v>
       </c>
       <c r="F52">
-        <v>5.850822603015416</v>
+        <v>6.070807163972463</v>
       </c>
       <c r="G52">
-        <v>-10.66247617178191</v>
+        <v>-9.983925377339428</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.962509849103776</v>
       </c>
       <c r="E53">
-        <v>-21.47851363597799</v>
+        <v>-21.52745507822977</v>
       </c>
       <c r="F53">
-        <v>5.532804073406658</v>
+        <v>5.822891710927823</v>
       </c>
       <c r="G53">
-        <v>-10.74866990445751</v>
+        <v>-10.65215459304094</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.085352696764875</v>
       </c>
       <c r="E54">
-        <v>-19.25694013227058</v>
+        <v>-20.8201175042869</v>
       </c>
       <c r="F54">
-        <v>5.731522786399037</v>
+        <v>6.210746582796996</v>
       </c>
       <c r="G54">
-        <v>-10.27209022770045</v>
+        <v>-10.62270539405319</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.199800577805251</v>
       </c>
       <c r="E55">
-        <v>-20.21074587907408</v>
+        <v>-20.56930922559183</v>
       </c>
       <c r="F55">
-        <v>5.96535102339167</v>
+        <v>6.294935218678315</v>
       </c>
       <c r="G55">
-        <v>-9.873141041360128</v>
+        <v>-10.3431990781286</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.309051524896468</v>
       </c>
       <c r="E56">
-        <v>-18.19971942347885</v>
+        <v>-19.81590007842263</v>
       </c>
       <c r="F56">
-        <v>5.781947166942248</v>
+        <v>6.017987144900356</v>
       </c>
       <c r="G56">
-        <v>-10.59313087932505</v>
+        <v>-10.26925756981909</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.412594303253677</v>
       </c>
       <c r="E57">
-        <v>-19.19863735169264</v>
+        <v>-20.12245275951955</v>
       </c>
       <c r="F57">
-        <v>5.913496880711227</v>
+        <v>6.197794230086823</v>
       </c>
       <c r="G57">
-        <v>-10.32241624581104</v>
+        <v>-10.94346930675114</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.515029822146283</v>
       </c>
       <c r="E58">
-        <v>-18.77888889593752</v>
+        <v>-19.81182162490165</v>
       </c>
       <c r="F58">
-        <v>6.455305491125493</v>
+        <v>6.276409610082107</v>
       </c>
       <c r="G58">
-        <v>-11.82859004547628</v>
+        <v>-11.16070675343308</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.61532764578649</v>
       </c>
       <c r="E59">
-        <v>-17.62826246445039</v>
+        <v>-18.85907079377466</v>
       </c>
       <c r="F59">
-        <v>6.022529911737308</v>
+        <v>6.694156948048703</v>
       </c>
       <c r="G59">
-        <v>-10.91801585236008</v>
+        <v>-11.25274072175901</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.717493375702105</v>
       </c>
       <c r="E60">
-        <v>-17.75292525557645</v>
+        <v>-18.44289825297021</v>
       </c>
       <c r="F60">
-        <v>6.215184975341195</v>
+        <v>6.466281359212587</v>
       </c>
       <c r="G60">
-        <v>-11.33658086818573</v>
+        <v>-11.33613182011605</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.819147090191624</v>
       </c>
       <c r="E61">
-        <v>-18.64425424442055</v>
+        <v>-17.87317733627553</v>
       </c>
       <c r="F61">
-        <v>6.703605306645034</v>
+        <v>6.438832576953422</v>
       </c>
       <c r="G61">
-        <v>-10.99884189415635</v>
+        <v>-11.57227497375455</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.923250384465476</v>
       </c>
       <c r="E62">
-        <v>-16.85918740416394</v>
+        <v>-18.46819961636107</v>
       </c>
       <c r="F62">
-        <v>6.399748546154536</v>
+        <v>6.340379454395896</v>
       </c>
       <c r="G62">
-        <v>-11.6556621559947</v>
+        <v>-11.4477829232996</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.026797166706254</v>
       </c>
       <c r="E63">
-        <v>-17.06368737658718</v>
+        <v>-17.91673621665034</v>
       </c>
       <c r="F63">
-        <v>5.994110282882064</v>
+        <v>6.655197172360237</v>
       </c>
       <c r="G63">
-        <v>-11.54533470031885</v>
+        <v>-11.26891428450095</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.131964751959766</v>
       </c>
       <c r="E64">
-        <v>-16.72433678565809</v>
+        <v>-17.29828567148144</v>
       </c>
       <c r="F64">
-        <v>6.201955947918488</v>
+        <v>6.457248841052461</v>
       </c>
       <c r="G64">
-        <v>-11.78018161926785</v>
+        <v>-12.26071265796357</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.235768387519244</v>
       </c>
       <c r="E65">
-        <v>-15.9645399994713</v>
+        <v>-18.07697126277354</v>
       </c>
       <c r="F65">
-        <v>5.757061353427345</v>
+        <v>6.683605204071843</v>
       </c>
       <c r="G65">
-        <v>-11.68516487524658</v>
+        <v>-12.04059555999763</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.340242456875079</v>
       </c>
       <c r="E66">
-        <v>-15.82488411546262</v>
+        <v>-16.69405572188876</v>
       </c>
       <c r="F66">
-        <v>5.755671352925448</v>
+        <v>6.641857143705553</v>
       </c>
       <c r="G66">
-        <v>-11.80950550251524</v>
+        <v>-12.3090323188559</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.443378152866448</v>
       </c>
       <c r="E67">
-        <v>-16.96258160009555</v>
+        <v>-17.47691944377364</v>
       </c>
       <c r="F67">
-        <v>6.93554652269409</v>
+        <v>6.786731975515965</v>
       </c>
       <c r="G67">
-        <v>-12.20203095178912</v>
+        <v>-12.64813410156183</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.547555140305765</v>
       </c>
       <c r="E68">
-        <v>-16.24301281880106</v>
+        <v>-18.0145360369274</v>
       </c>
       <c r="F68">
-        <v>6.354110472464701</v>
+        <v>6.693772585573804</v>
       </c>
       <c r="G68">
-        <v>-12.05248228012097</v>
+        <v>-12.4401465229662</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.651433789690119</v>
       </c>
       <c r="E69">
-        <v>-15.4268320356684</v>
+        <v>-16.36585235015551</v>
       </c>
       <c r="F69">
-        <v>6.051410112868511</v>
+        <v>6.763703361718139</v>
       </c>
       <c r="G69">
-        <v>-12.50725179656388</v>
+        <v>-12.81780639253828</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.757333503357341</v>
       </c>
       <c r="E70">
-        <v>-16.49344730847689</v>
+        <v>-16.41260089682778</v>
       </c>
       <c r="F70">
-        <v>6.318576824354213</v>
+        <v>7.156064552258541</v>
       </c>
       <c r="G70">
-        <v>-12.04305096528557</v>
+        <v>-12.36182810134969</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.864218076295568</v>
       </c>
       <c r="E71">
-        <v>-16.03294754320255</v>
+        <v>-17.35879796048419</v>
       </c>
       <c r="F71">
-        <v>6.269764446776849</v>
+        <v>6.84687476242882</v>
       </c>
       <c r="G71">
-        <v>-11.66320459711843</v>
+        <v>-13.33981563592531</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.974108807720592</v>
       </c>
       <c r="E72">
-        <v>-17.52428266572199</v>
+        <v>-16.16096197586774</v>
       </c>
       <c r="F72">
-        <v>6.430257317599642</v>
+        <v>6.999789728250803</v>
       </c>
       <c r="G72">
-        <v>-12.18836500922694</v>
+        <v>-12.86884906003914</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.086140745358024</v>
       </c>
       <c r="E73">
-        <v>-15.62231953951676</v>
+        <v>-17.259270404296</v>
       </c>
       <c r="F73">
-        <v>6.004463218682251</v>
+        <v>6.799387772695935</v>
       </c>
       <c r="G73">
-        <v>-11.59864871561397</v>
+        <v>-13.23630091825997</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.201838410972167</v>
       </c>
       <c r="E74">
-        <v>-17.43592309478626</v>
+        <v>-16.86826632412002</v>
       </c>
       <c r="F74">
-        <v>6.088464643530538</v>
+        <v>6.678530625362293</v>
       </c>
       <c r="G74">
-        <v>-12.73850372021092</v>
+        <v>-12.99577562982529</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.319916532521792</v>
       </c>
       <c r="E75">
-        <v>-16.83376559764467</v>
+        <v>-16.37252240754318</v>
       </c>
       <c r="F75">
-        <v>5.409915769201351</v>
+        <v>6.831755400592924</v>
       </c>
       <c r="G75">
-        <v>-12.10997609750646</v>
+        <v>-13.35622808179735</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.441640547831538</v>
       </c>
       <c r="E76">
-        <v>-16.89669505563847</v>
+        <v>-17.30622245832319</v>
       </c>
       <c r="F76">
-        <v>5.775515722426912</v>
+        <v>6.605748608617523</v>
       </c>
       <c r="G76">
-        <v>-12.97570422540881</v>
+        <v>-13.23564823211219</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.565653343903774</v>
       </c>
       <c r="E77">
-        <v>-17.61174098980023</v>
+        <v>-18.3716706787494</v>
       </c>
       <c r="F77">
-        <v>5.722379267006936</v>
+        <v>6.651963226019707</v>
       </c>
       <c r="G77">
-        <v>-11.9801724871809</v>
+        <v>-12.95789894729742</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.693145906528505</v>
       </c>
       <c r="E78">
-        <v>-17.12230995443713</v>
+        <v>-18.13580565440106</v>
       </c>
       <c r="F78">
-        <v>5.50681321777642</v>
+        <v>6.895286210183229</v>
       </c>
       <c r="G78">
-        <v>-11.91881476780056</v>
+        <v>-12.38021688087719</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.822750997637422</v>
       </c>
       <c r="E79">
-        <v>-18.95863572886477</v>
+        <v>-18.46655909788776</v>
       </c>
       <c r="F79">
-        <v>5.53798302640896</v>
+        <v>6.859048449780362</v>
       </c>
       <c r="G79">
-        <v>-11.84704800973545</v>
+        <v>-12.8198571324146</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.955291699346294</v>
       </c>
       <c r="E80">
-        <v>-18.2263082823804</v>
+        <v>-18.2081919745815</v>
       </c>
       <c r="F80">
-        <v>6.32140487066737</v>
+        <v>6.666491133530005</v>
       </c>
       <c r="G80">
-        <v>-11.51420157106982</v>
+        <v>-12.67154986979952</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.089025986819141</v>
       </c>
       <c r="E81">
-        <v>-17.95387007910563</v>
+        <v>-19.58677571605449</v>
       </c>
       <c r="F81">
-        <v>5.952070637189989</v>
+        <v>6.687606218627365</v>
       </c>
       <c r="G81">
-        <v>-11.54318605752036</v>
+        <v>-12.36204870926763</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.224070118307582</v>
       </c>
       <c r="E82">
-        <v>-20.32508378684661</v>
+        <v>-20.42349828239975</v>
       </c>
       <c r="F82">
-        <v>5.832012036032645</v>
+        <v>6.886937923497815</v>
       </c>
       <c r="G82">
-        <v>-11.72090988481581</v>
+        <v>-12.45078400180269</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.358764461007187</v>
       </c>
       <c r="E83">
-        <v>-20.31481704845163</v>
+        <v>-20.69233980466722</v>
       </c>
       <c r="F83">
-        <v>5.447162481100828</v>
+        <v>6.757119497600688</v>
       </c>
       <c r="G83">
-        <v>-11.17198778081128</v>
+        <v>-12.90905452674228</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.491431682331809</v>
       </c>
       <c r="E84">
-        <v>-21.60881648808316</v>
+        <v>-22.16822498105829</v>
       </c>
       <c r="F84">
-        <v>5.915776547803731</v>
+        <v>6.732727391057853</v>
       </c>
       <c r="G84">
-        <v>-10.07784299788784</v>
+        <v>-12.09819119642218</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.619309787212778</v>
       </c>
       <c r="E85">
-        <v>-22.93524004852763</v>
+        <v>-22.19546174092652</v>
       </c>
       <c r="F85">
-        <v>6.13279058325434</v>
+        <v>6.828904159992487</v>
       </c>
       <c r="G85">
-        <v>-11.46742486023084</v>
+        <v>-12.11262730863874</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.738562860760521</v>
       </c>
       <c r="E86">
-        <v>-24.09055545560048</v>
+        <v>-23.24259845262156</v>
       </c>
       <c r="F86">
-        <v>5.610485054971584</v>
+        <v>6.965657677785853</v>
       </c>
       <c r="G86">
-        <v>-11.52009663235656</v>
+        <v>-12.61113723996116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.845389257172803</v>
       </c>
       <c r="E87">
-        <v>-24.38412104488467</v>
+        <v>-24.66081213655607</v>
       </c>
       <c r="F87">
-        <v>5.94185686711347</v>
+        <v>6.768408488566039</v>
       </c>
       <c r="G87">
-        <v>-11.5103011186507</v>
+        <v>-12.43088099041234</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.933818728122005</v>
       </c>
       <c r="E88">
-        <v>-26.13823400113732</v>
+        <v>-26.25238501440024</v>
       </c>
       <c r="F88">
-        <v>5.956631628109802</v>
+        <v>7.181997422170582</v>
       </c>
       <c r="G88">
-        <v>-10.16616187666061</v>
+        <v>-12.2187527708952</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.997846288251877</v>
       </c>
       <c r="E89">
-        <v>-26.72745009179075</v>
+        <v>-26.72738779362088</v>
       </c>
       <c r="F89">
-        <v>6.263352883079181</v>
+        <v>6.983843655746912</v>
       </c>
       <c r="G89">
-        <v>-10.40763356000957</v>
+        <v>-12.22968395849819</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.029733912009552</v>
       </c>
       <c r="E90">
-        <v>-29.96242377160162</v>
+        <v>-29.83047417120616</v>
       </c>
       <c r="F90">
-        <v>6.356784442440937</v>
+        <v>7.225380679789998</v>
       </c>
       <c r="G90">
-        <v>-10.29009131165617</v>
+        <v>-11.63411307013966</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.022821020994075</v>
       </c>
       <c r="E91">
-        <v>-30.1706782470625</v>
+        <v>-31.10902366470933</v>
       </c>
       <c r="F91">
-        <v>6.507537369341613</v>
+        <v>7.264552517533581</v>
       </c>
       <c r="G91">
-        <v>-10.2932855576634</v>
+        <v>-11.6004018306069</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.969356583540487</v>
       </c>
       <c r="E92">
-        <v>-32.10022492628158</v>
+        <v>-31.90808906397236</v>
       </c>
       <c r="F92">
-        <v>5.250536224167921</v>
+        <v>6.901773983681954</v>
       </c>
       <c r="G92">
-        <v>-9.877561031952883</v>
+        <v>-12.24753100852304</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.864032631719468</v>
       </c>
       <c r="E93">
-        <v>-35.01289279444046</v>
+        <v>-34.48531451305882</v>
       </c>
       <c r="F93">
-        <v>5.687057680951565</v>
+        <v>6.981824096018888</v>
       </c>
       <c r="G93">
-        <v>-10.36851546842862</v>
+        <v>-11.97483612523667</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.701946481705706</v>
       </c>
       <c r="E94">
-        <v>-36.26576090571655</v>
+        <v>-36.52084699207619</v>
       </c>
       <c r="F94">
-        <v>5.674411824180428</v>
+        <v>6.943811972639224</v>
       </c>
       <c r="G94">
-        <v>-10.81632735053622</v>
+        <v>-11.59648440834794</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.483781213507973</v>
       </c>
       <c r="E95">
-        <v>-38.50600724754039</v>
+        <v>-39.26285525368655</v>
       </c>
       <c r="F95">
-        <v>5.614088453173762</v>
+        <v>7.013191056093294</v>
       </c>
       <c r="G95">
-        <v>-9.927372733379029</v>
+        <v>-11.7707372507095</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.210522959013224</v>
       </c>
       <c r="E96">
-        <v>-41.42752145582116</v>
+        <v>-40.04665137151385</v>
       </c>
       <c r="F96">
-        <v>5.228943999446549</v>
+        <v>7.164515556501901</v>
       </c>
       <c r="G96">
-        <v>-9.701162157537427</v>
+        <v>-11.57564936113856</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.892667115565937</v>
       </c>
       <c r="E97">
-        <v>-41.78319832046814</v>
+        <v>-44.17124914691998</v>
       </c>
       <c r="F97">
-        <v>5.401734812731303</v>
+        <v>6.811182067776995</v>
       </c>
       <c r="G97">
-        <v>-9.337597698012765</v>
+        <v>-10.97755649350501</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.537004560159436</v>
       </c>
       <c r="E98">
-        <v>-45.11884168958154</v>
+        <v>-46.24394456087193</v>
       </c>
       <c r="F98">
-        <v>5.473217949388483</v>
+        <v>6.91243672889079</v>
       </c>
       <c r="G98">
-        <v>-8.522487991615217</v>
+        <v>-11.75033819784684</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.166420411343954</v>
       </c>
       <c r="E99">
-        <v>-48.71375239055585</v>
+        <v>-48.21359568694638</v>
       </c>
       <c r="F99">
-        <v>5.237292286131962</v>
+        <v>6.755757661590486</v>
       </c>
       <c r="G99">
-        <v>-10.74867643131899</v>
+        <v>-11.25078788480486</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.78863491115688</v>
       </c>
       <c r="E100">
-        <v>-50.27703463115812</v>
+        <v>-50.35120683220823</v>
       </c>
       <c r="F100">
-        <v>5.233755157322008</v>
+        <v>6.47028568723772</v>
       </c>
       <c r="G100">
-        <v>-8.457806794370384</v>
+        <v>-10.8942136939229</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.4417679707217</v>
       </c>
       <c r="E101">
-        <v>-52.86369513807175</v>
+        <v>-53.05731992664092</v>
       </c>
       <c r="F101">
-        <v>5.006118138297898</v>
+        <v>6.185186478216214</v>
       </c>
       <c r="G101">
-        <v>-10.56539824490595</v>
+        <v>-11.30480419039499</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.120441130294607</v>
       </c>
       <c r="E102">
-        <v>-54.79224868063278</v>
+        <v>-55.91547793446426</v>
       </c>
       <c r="F102">
-        <v>4.088886793995673</v>
+        <v>6.142765783518851</v>
       </c>
       <c r="G102">
-        <v>-9.336127848807967</v>
+        <v>-11.16015066483518</v>
       </c>
     </row>
   </sheetData>
